--- a/Admin/Course Index.xlsx
+++ b/Admin/Course Index.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/851caa7714272873/CLASSES-Informatics/Admin/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="151" documentId="14_{A7AB479B-D60E-EA45-B3DD-6B710ED86952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65310BB0-4D6D-2347-B2E1-166B7048C942}"/>
+  <xr:revisionPtr revIDLastSave="173" documentId="14_{A7AB479B-D60E-EA45-B3DD-6B710ED86952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDD0207E-9D92-5A75-81FE-5A6F695FE37F}"/>
   <bookViews>
     <workbookView xWindow="5680" yWindow="2620" windowWidth="27040" windowHeight="16960" xr2:uid="{FC2EA60D-F956-465D-A12E-C3B3EB9E01DA}"/>
   </bookViews>
